--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>85</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>06/09 19:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>01/09 15:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>65</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>06/09 21:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>02/09 15:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F7" t="n">
+        <v>1.65</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>07/09 19:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>01/09 23:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>01/09 13:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>01/09 18:15</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>42</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>01/09 17:10</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F14" t="n">
+        <v>2.75</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>01/09 02:45</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="F15" t="n">
+        <v>3.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>06/09 23:20</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>02/09 00:40</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="F17" t="n">
+        <v>1.45</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>01/09 17:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>20</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>01/09 19:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F19" t="n">
+        <v>1.72</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>02/09 00:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,52 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45901.08007941419</v>
+        <v>45901.08007940972</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Real Socie</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Real Sociedad B – CadixLaLiga2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>07/09 14:15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>+12,6%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45901.14108986031</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,10 +1322,8 @@
           <t>07/09 14:15</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1338,7 +1336,142 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45901.14108986031</v>
+        <v>45901.14108986111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 5.5 - aces1er participant | Lorenzo Mu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti – Jaume MunarATP - US Open</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Moins que 5.5 - aces1er participant</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>01/09 18:10</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>+5,84%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>45901.18787912601</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball | Plus que 85.51re mi-temps | MIN Lynx –</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MIN Lynx – DAL WingsUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Plus que 85.51re mi-temps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>02/09 00:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>48,2%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>+1,31%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>45901.18787912601</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Alexander BublikUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>01/09 23:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>+1,26%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>45901.18787912601</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,10 +1365,8 @@
           <t>01/09 18:10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1381,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45901.18787912601</v>
+        <v>45901.18787912037</v>
       </c>
     </row>
     <row r="23">
@@ -1410,10 +1408,8 @@
           <t>02/09 00:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1426,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45901.18787912601</v>
+        <v>45901.18787912037</v>
       </c>
     </row>
     <row r="24">
@@ -1455,10 +1451,8 @@
           <t>01/09 23:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1471,7 +1465,97 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45901.18787912601</v>
+        <v>45901.18787912037</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 2.51re équipe | Arménie – </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Arménie – PortugalCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>06/09 16:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+3,00%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45901.22391552994</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Platens</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CA Platense – Godoy CruzLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>01/09 22:15</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+0,98%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45901.22391552994</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,10 +1494,8 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1510,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45901.22391552994</v>
+        <v>45901.22391553241</v>
       </c>
     </row>
     <row r="26">
@@ -1539,10 +1537,8 @@
           <t>01/09 22:15</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>60</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1555,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45901.22391552994</v>
+        <v>45901.22391553241</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | H 2 (−5.5) | T.Machac /</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T.Machac / M.Vocel – M.Arevalo / M.PavicATP - US Open, Doubles</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>H 2 (−5.5)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>01/09 17:40</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+1,87%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45901.27435965403</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>01/09 17:40</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F27" t="n">
+        <v>2.95</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,97 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45901.27435965403</v>
+        <v>45901.27435965278</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Lulea HFInternational - ChampionsLeague</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>04/09 16:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+41,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45901.30679033999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Jiri Lehec</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka – Carlos AlcarazUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>02/09 15:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45901.30679033999</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>04/09 16:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>100</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45901.30679033999</v>
+        <v>45901.30679033565</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>02/09 15:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>55</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,547 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45901.30679033999</v>
+        <v>45901.30679033565</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Lausanne – Belfast GiantsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>05/09 16:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+288%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Odense Bul</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Odense Bulldogs – ZSC LionsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>04/09 17:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+268%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Tychy – Fr</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tychy – Frölunda HCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>04/09 15:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+199%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Pinguins B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pinguins Bremerhaven – GrenobleLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>05/09 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+188%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Brynäs IF </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brynäs IF – KACEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>04/09 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+157%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Berlin – L</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Berlin – Lukko RaumaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>05/09 17:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+149%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bolzano – Kometa BrnoEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+146%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EV Zug – E</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EV Zug – ERC IngolstadtLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+142%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KalPa – St</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>KalPa – Storhamar IL DragonsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>04/09 15:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ilves Tamp</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ilves Tampere – SalzbourgEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>04/09 15:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Luleå HFEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>04/09 16:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+94,9%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45901.35478752245</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Bern – Mou</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bern – Mountfield HKEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+78,8%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45901.35478752245</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>05/09 16:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>250</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>04/09 17:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>250</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="32">
@@ -1799,10 +1795,8 @@
           <t>04/09 15:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>200</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1815,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="33">
@@ -1844,10 +1838,8 @@
           <t>05/09 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>175</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1860,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="34">
@@ -1889,10 +1881,8 @@
           <t>04/09 17:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>175</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1905,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="35">
@@ -1934,10 +1924,8 @@
           <t>05/09 17:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>150</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1950,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="36">
@@ -1979,10 +1967,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>150</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1995,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="37">
@@ -2024,10 +2010,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>150</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2040,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="38">
@@ -2069,10 +2053,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>150</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2085,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="39">
@@ -2114,10 +2096,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>150</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2130,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="40">
@@ -2159,10 +2139,8 @@
           <t>04/09 16:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>125</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2175,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
       </c>
     </row>
     <row r="41">
@@ -2204,10 +2182,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>110</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2220,7 +2196,187 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45901.35478752245</v>
+        <v>45901.35478752315</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Brynas IF </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brynas IF – KAC KlagenfurtLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>04/09 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+171%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45901.39293895734</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KalPa – St</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>KalPa – StorhamarLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>04/09 15:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45901.39293895734</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Bolzano</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HC Bolzano-Bozen Foxes – HC Kometa BrnoLigue des Champions (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,70%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45901.39293895734</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball | Plus que 3.5 | Etats-Unis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Etats-Unis – CanadaChampionnat du Monde (F) stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>01/09 10:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>51,5%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+3,08%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45901.39293895734</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>04/09 17:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>175</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45901.39293895734</v>
+        <v>45901.39293895834</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>150</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45901.39293895734</v>
+        <v>45901.39293895834</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>125</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45901.39293895734</v>
+        <v>45901.39293895834</v>
       </c>
     </row>
     <row r="45">
@@ -2360,10 +2354,8 @@
           <t>01/09 10:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2376,7 +2368,187 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45901.39293895734</v>
+        <v>45901.39293895834</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ilves Tamp</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ilves Tampere – RB SalzbourgLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>04/09 15:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+126%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45901.43345299562</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | SC Bern – </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SC Bern – Mountfield HKLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+79,3%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45901.43345299562</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | L.Musetti </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>L.Musetti – J.MunarATP - US Open H</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>01/09 18:10</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>64,0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+5,65%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45901.43345299562</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Plus que 6.5 - aces | Ekaterina </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova – Iga SwiatekUS Open (F)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - aces</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>01/09 17:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>65,0%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+3,92%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45901.43345299562</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>140</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45901.43345299562</v>
+        <v>45901.43345299768</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>110</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45901.43345299562</v>
+        <v>45901.43345299768</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>01/09 18:10</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F48" t="n">
+        <v>1.65</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45901.43345299562</v>
+        <v>45901.43345299768</v>
       </c>
     </row>
     <row r="49">
@@ -2532,10 +2526,8 @@
           <t>01/09 17:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F49" t="n">
+        <v>1.6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2548,7 +2540,52 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45901.43345299562</v>
+        <v>45901.43345299768</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Cabral F /</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cabral F / Miedler L – Pavlasek A / Zielinski JUS Open - Doubles (H)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>01/09 16:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+2,17%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45901.47089288018</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>01/09 16:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
+      <c r="F50" t="n">
+        <v>5.2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45901.47089288018</v>
+        <v>45901.47089288195</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Lulea HFLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>04/09 16:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+82,5%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45901.53158307484</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Brésil – C</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Brésil – ChiliCDM - Qualifs Amérique du sud</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>05/09 00:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+5,97%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45901.53158307484</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>04/09 16:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>110</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45901.53158307484</v>
+        <v>45901.5315830787</v>
       </c>
     </row>
     <row r="52">
@@ -2657,23 +2655,111 @@
           <t>05/09 00:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>50</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+5,97%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45901.5315830787</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Connah's Q</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Connah's Quay – Bala TownCymru Premier</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02/09 18:45</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+58,9%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45901.56281131809</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 2.52e équipe | Allemagne </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Allemagne – Irlande du NordCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>07/09 18:45</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>+5,97%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>45901.53158307484</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+16,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45901.56281131809</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -2698,10 +2698,8 @@
           <t>02/09 18:45</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>55</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45901.56281131809</v>
+        <v>45901.56281131945</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>07/09 18:45</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>50</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45901.56281131809</v>
+        <v>45901.56281131945</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2758,6 +2758,51 @@
         <v>45901.56281131945</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Huesca – E</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Huesca – EibarLaLiga2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>01/09 17:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+38,6%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45901.72054961052</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>01/09 17:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>60</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,142 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45901.72054961052</v>
+        <v>45901.72054960648</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zug – Ingo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Zug – IngolstadtEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+163%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45901.77024335028</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Eisbären B</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Eisbären Berlin – LukkoEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>05/09 17:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+135%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45901.77024335028</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Eibar – FC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Eibar – FC AndorraLaLiga2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>08/09 18:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+6,05%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45901.77024335028</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -2827,10 +2827,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>175</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45901.77024335028</v>
+        <v>45901.77024334491</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>05/09 17:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>150</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45901.77024335028</v>
+        <v>45901.77024334491</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>08/09 18:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>50</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45901.77024335028</v>
+        <v>45901.77024334491</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2930,6 +2930,51 @@
         <v>45901.77024334491</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Belgique –</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Belgique – KazakhstanCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>07/09 18:45</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,40%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+8,22%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45901.84843382137</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -2956,10 +2956,8 @@
           <t>07/09 18:45</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>45</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45901.84843382137</v>
+        <v>45901.84843381945</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2973,6 +2973,96 @@
         <v>45901.84843381945</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Lausanne – Belfast GiantsLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>05/09 16:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+211%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45901.93027115145</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – Sparta PragueRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+104%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45901.93027115145</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-01.xlsx
+++ b/data/valuebets_database_2025-09-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>05/09 16:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>200</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45901.93027115145</v>
+        <v>45901.93027114584</v>
       </c>
     </row>
     <row r="61">
@@ -3044,23 +3042,111 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="n">
+        <v>125</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+104%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45901.93027114584</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – Sparta PragueExtraliga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>+104%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>45901.93027115145</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+96,3%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45901.97189237887</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – Brûleurs de loups de GrenobleInternational - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>05/09 17:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+33,8%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45901.97189237887</v>
       </c>
     </row>
   </sheetData>
